--- a/entretiens/FPPN_PBC_complementaire_placements_provisions_20261019.xlsx
+++ b/entretiens/FPPN_PBC_complementaire_placements_provisions_20261019.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PBC Placements et provisions'!$B$12:$P$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'PBC Placements et provisions'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Placements et provisions'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'PBC Placements et provisions'!$A$1:$N$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -816,7 +816,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="21" customHeight="1" s="35">
+    <row r="11" ht="30" customHeight="1" s="35">
       <c r="B11" s="46">
         <f>80</f>
         <v/>
@@ -850,7 +850,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" s="35">
+    <row r="12" ht="42" customHeight="1" s="35">
       <c r="B12" s="46">
         <f>+B11+1</f>
         <v/>
@@ -884,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" s="35">
+    <row r="13" ht="42" customHeight="1" s="35">
       <c r="B13" s="46">
         <f>+B12+1</f>
         <v/>
@@ -918,7 +918,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="21" customHeight="1" s="35">
+    <row r="14" ht="30" customHeight="1" s="35">
       <c r="B14" s="46">
         <f>+B13+1</f>
         <v/>
@@ -948,7 +948,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" s="35">
+    <row r="15" ht="42" customHeight="1" s="35">
       <c r="B15" s="46">
         <f>+B14+1</f>
         <v/>
@@ -978,7 +978,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="21" customHeight="1" s="35">
+    <row r="16" ht="30" customHeight="1" s="35">
       <c r="B16" s="46">
         <f>+B15+1</f>
         <v/>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="21" customHeight="1" s="35">
+    <row r="17" ht="30" customHeight="1" s="35">
       <c r="B17" s="46">
         <f>+B16+1</f>
         <v/>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1" s="35">
+    <row r="18" ht="42" customHeight="1" s="35">
       <c r="B18" s="46">
         <f>+B17+1</f>
         <v/>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="21" customHeight="1" s="35">
+    <row r="19" ht="30" customHeight="1" s="35">
       <c r="B19" s="46">
         <f>+B18+1</f>
         <v/>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="21" customHeight="1" s="35">
+    <row r="20" ht="30" customHeight="1" s="35">
       <c r="B20" s="46">
         <f>+B19+1</f>
         <v/>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="21" customHeight="1" s="35">
+    <row r="21" ht="30" customHeight="1" s="35">
       <c r="B21" s="46">
         <f>+B20+1</f>
         <v/>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="21" customHeight="1" s="35">
+    <row r="22" ht="30" customHeight="1" s="35">
       <c r="B22" s="46">
         <f>+B21+1</f>
         <v/>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="36" customHeight="1" s="35">
+    <row r="25" ht="42" customHeight="1" s="35">
       <c r="B25" s="46">
         <f>+B22+1</f>
         <v/>
@@ -1244,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="21" customHeight="1" s="35">
+    <row r="26" ht="30" customHeight="1" s="35">
       <c r="B26" s="46">
         <f>+B25+1</f>
         <v/>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="21" customHeight="1" s="35">
+    <row r="27" ht="30" customHeight="1" s="35">
       <c r="B27" s="46">
         <f>+B26+1</f>
         <v/>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="21" customHeight="1" s="35">
+    <row r="28" ht="30" customHeight="1" s="35">
       <c r="B28" s="46">
         <f>+B27+1</f>
         <v/>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="21" customHeight="1" s="35">
+    <row r="29" ht="30" customHeight="1" s="35">
       <c r="B29" s="46">
         <f>+B28+1</f>
         <v/>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="21" customHeight="1" s="35">
+    <row r="30" ht="30" customHeight="1" s="35">
       <c r="B30" s="46">
         <f>+B29+1</f>
         <v/>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="21" customHeight="1" s="35">
+    <row r="31" ht="30" customHeight="1" s="35">
       <c r="B31" s="46">
         <f>+B30+1</f>
         <v/>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="21" customHeight="1" s="35">
+    <row r="32" ht="30" customHeight="1" s="35">
       <c r="B32" s="46">
         <f>+B31+1</f>
         <v/>
@@ -1760,7 +1760,7 @@
     <mergeCell ref="C5:M5"/>
     <mergeCell ref="C4:M4"/>
   </mergeCells>
-  <conditionalFormatting sqref="M11:M29">
+  <conditionalFormatting sqref="M11:M32">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="equal" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>"Partiellement Reçu"</formula>
     </cfRule>
@@ -1771,7 +1771,7 @@
       <formula>"Reçu"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E29">
+  <conditionalFormatting sqref="E11:E32">
     <cfRule type="cellIs" rank="0" priority="5" equalAverage="0" operator="equal" aboveAverage="0" dxfId="8" text="" percent="0" bottom="0">
       <formula>"Faible"</formula>
     </cfRule>
